--- a/docs/Mapping_casi_uso/cittadinanza/Citt_039.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_039.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="149">
   <si>
     <t>Sezione</t>
   </si>
@@ -326,7 +326,7 @@
     <t>flagFirmatario</t>
   </si>
   <si>
-    <t>Atto collegato</t>
+    <t>Atto di nascita</t>
   </si>
   <si>
     <t>Id atto</t>
@@ -405,6 +405,12 @@
   </si>
   <si>
     <t>tipologia</t>
+  </si>
+  <si>
+    <t>Atto collegato di Cittadinanza</t>
+  </si>
+  <si>
+    <t>evento.eventoCollegatoCittadinanza</t>
   </si>
   <si>
     <t>Autorità mittente</t>
@@ -511,10 +517,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.73828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="45.0546875" customWidth="true" bestFit="true"/>
@@ -1862,22 +1868,22 @@
         <v>131</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="E59" s="2" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60">
@@ -1885,22 +1891,22 @@
         <v>131</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61">
@@ -1908,22 +1914,22 @@
         <v>131</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62">
@@ -1931,22 +1937,22 @@
         <v>131</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63">
@@ -1954,22 +1960,22 @@
         <v>131</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64">
@@ -1977,22 +1983,22 @@
         <v>131</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65">
@@ -2000,21 +2006,320 @@
         <v>131</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D65" s="2" t="s">
+      <c r="C77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="2" t="s">
+      <c r="B78" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>18</v>
       </c>
     </row>
